--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>##var#column</t>
   </si>
@@ -41,18 +41,6 @@
     <t>##</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">##======== </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单局与撤离</t>
-    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -60,56 +48,6 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> ==========</t>
-    </r>
-  </si>
-  <si>
-    <t>runTimeLimitMs</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单局时间上限，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>extractionRevealTimeMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小地图标记撤离点的时间，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>escapeProtectionMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>逃跑返回地图后的保护时间，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -119,7 +57,7 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>敌人警惕与追击</t>
+      <t>单局与撤离</t>
     </r>
     <r>
       <rPr>
@@ -132,60 +70,51 @@
     </r>
   </si>
   <si>
-    <t>enemyLoseTargetMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>enemyFrontViewAngle</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人正面视野角度</t>
-    </r>
-  </si>
-  <si>
-    <t>alertMax</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>警惕值满值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">##======== </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>队伍与库存</t>
-    </r>
+    <t>runTimeLimitMs</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单局时间上限，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>extractionRevealTimeMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小地图标记撤离点的时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>escapeProtectionMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逃跑返回地图后的保护时间，毫秒</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -193,95 +122,6 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> ==========</t>
-    </r>
-  </si>
-  <si>
-    <t>warehouseSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仓库格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>backpackSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>共享背包格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>secureSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>保险箱格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>minPlayerPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最少出战人数</t>
-    </r>
-  </si>
-  <si>
-    <t>maxPlayerPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最多出战人数</t>
-    </r>
-  </si>
-  <si>
-    <t>maxEnemyPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人队伍人数上限</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -291,7 +131,7 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>战斗与计时</t>
+      <t>敌人警惕与追击</t>
     </r>
     <r>
       <rPr>
@@ -304,6 +144,190 @@
     </r>
   </si>
   <si>
+    <t>enemyLoseTargetMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>enemyFrontViewAngle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人正面视野角度</t>
+    </r>
+  </si>
+  <si>
+    <t>alertMax</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>警惕值满值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">##======== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>队伍与库存</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ==========</t>
+    </r>
+  </si>
+  <si>
+    <t>warehouseSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>backpackSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>共享背包格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>secureSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>保险箱格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>minPlayerPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最少出战人数</t>
+    </r>
+  </si>
+  <si>
+    <t>maxPlayerPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多出战人数</t>
+    </r>
+  </si>
+  <si>
+    <t>maxEnemyPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人队伍人数上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">##======== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗与计时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ==========</t>
+    </r>
+  </si>
+  <si>
     <t>reviveHp</t>
   </si>
   <si>
@@ -423,7 +447,36 @@
     </r>
   </si>
   <si>
-    <r>
+    <t>autoAdvanceDelayMs</t>
+  </si>
+  <si>
+    <t>敌人自动行动间隔</t>
+  </si>
+  <si>
+    <t>registerFrameout</t>
+  </si>
+  <si>
+    <r>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时间注册超时帧数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -476,7 +529,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -503,6 +556,12 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -658,18 +717,18 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF375623"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -709,12 +768,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -998,156 +1051,156 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1171,11 +1224,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1648,14 +1698,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.0073529411765" style="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7867647058824" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.2794117647059" style="2" customWidth="1"/>
     <col min="6" max="6" width="28" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -1737,12 +1787,12 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="9"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:6">
       <c r="A7" s="5" t="s">
@@ -1803,12 +1853,12 @@
       <c r="F10" s="7"/>
     </row>
     <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="5" t="s">
@@ -1917,12 +1967,12 @@
       <c r="F18" s="7"/>
     </row>
     <row r="19" customHeight="1" spans="1:6">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="9"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="5" t="s">
@@ -2047,38 +2097,70 @@
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="9"/>
+      <c r="A28" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="8">
+        <v>600</v>
+      </c>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
-      <c r="A29" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="5"/>
+      <c r="A29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="8">
+        <v>600</v>
+      </c>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
-      <c r="A30" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="A30" s="7"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="8" t="s">
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:6">
+      <c r="A31" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="7"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:6">
+      <c r="A32" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t>##var#column</t>
   </si>
@@ -468,6 +468,18 @@
       </rPr>
       <t>时间注册超时帧数</t>
     </r>
+  </si>
+  <si>
+    <t>cardStateTextDurationMs</t>
+  </si>
+  <si>
+    <t>卡片状态文本动画时间</t>
+  </si>
+  <si>
+    <t>cardStateTextFloatPx</t>
+  </si>
+  <si>
+    <t>卡片状态文本浮动高度</t>
   </si>
   <si>
     <r>
@@ -1698,7 +1710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34" style="1" customWidth="1"/>
@@ -2129,38 +2141,70 @@
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
-      <c r="A30" s="7"/>
+      <c r="A30" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="8"/>
+      <c r="C30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="8">
+        <v>600</v>
+      </c>
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
-      <c r="A31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="8">
+        <v>32</v>
+      </c>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" customHeight="1" spans="1:6">
-      <c r="A32" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="A32" s="7"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="8" t="s">
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:6">
+      <c r="A34" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -42,12 +42,74 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">##======== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单局与撤离</t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve"> ==========</t>
+    </r>
+  </si>
+  <si>
+    <t>runTimeLimitMs</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单局时间上限，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>extractionRevealTimeMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小地图标记撤离点的时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>escapeProtectionMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逃跑返回地图后的保护时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -57,7 +119,7 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>单局与撤离</t>
+      <t>敌人警惕与追击</t>
     </r>
     <r>
       <rPr>
@@ -70,51 +132,60 @@
     </r>
   </si>
   <si>
-    <t>runTimeLimitMs</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单局时间上限，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>extractionRevealTimeMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小地图标记撤离点的时间，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>escapeProtectionMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>逃跑返回地图后的保护时间，毫秒</t>
-    </r>
-  </si>
-  <si>
+    <t>enemyLoseTargetMs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
+    </r>
+  </si>
+  <si>
+    <t>enemyFrontViewAngle</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人正面视野角度</t>
+    </r>
+  </si>
+  <si>
+    <t>alertMax</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>警惕值满值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">##======== </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF375623"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>队伍与库存</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -122,6 +193,95 @@
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve"> ==========</t>
+    </r>
+  </si>
+  <si>
+    <t>warehouseSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>backpackSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>共享背包格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>secureSlotCount</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>保险箱格子数</t>
+    </r>
+  </si>
+  <si>
+    <t>minPlayerPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最少出战人数</t>
+    </r>
+  </si>
+  <si>
+    <t>maxPlayerPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多出战人数</t>
+    </r>
+  </si>
+  <si>
+    <t>maxEnemyPartySize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人队伍人数上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -131,7 +291,7 @@
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>敌人警惕与追击</t>
+      <t>战斗与计时</t>
     </r>
     <r>
       <rPr>
@@ -144,232 +304,48 @@
     </r>
   </si>
   <si>
-    <t>enemyLoseTargetMs</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
-    </r>
-  </si>
-  <si>
-    <t>enemyFrontViewAngle</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人正面视野角度</t>
-    </r>
-  </si>
-  <si>
-    <t>alertMax</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>警惕值满值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
+    <t>reviveHp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>非全员阵亡结算时阵亡角色恢复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">##======== </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>队伍与库存</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
+      <t>HP</t>
+    </r>
+  </si>
+  <si>
+    <t>reviveMp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>非全员阵亡结算时阵亡角色恢复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> ==========</t>
-    </r>
-  </si>
-  <si>
-    <t>warehouseSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仓库格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>backpackSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>共享背包格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>secureSlotCount</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>保险箱格子数</t>
-    </r>
-  </si>
-  <si>
-    <t>minPlayerPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最少出战人数</t>
-    </r>
-  </si>
-  <si>
-    <t>maxPlayerPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最多出战人数</t>
-    </r>
-  </si>
-  <si>
-    <t>maxEnemyPartySize</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人队伍人数上限</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">##======== </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战斗与计时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> ==========</t>
-    </r>
-  </si>
-  <si>
-    <t>reviveHp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>非全员阵亡结算时阵亡角色恢复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>HP</t>
-    </r>
-  </si>
-  <si>
-    <t>reviveMp</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>非全员阵亡结算时阵亡角色恢复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
       <t>MP</t>
     </r>
   </si>
@@ -450,7 +426,15 @@
     <t>autoAdvanceDelayMs</t>
   </si>
   <si>
-    <t>敌人自动行动间隔</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人自动行动间隔</t>
+    </r>
   </si>
   <si>
     <t>registerFrameout</t>
@@ -463,7 +447,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体-简"/>
+        <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
       <t>时间注册超时帧数</t>
@@ -473,22 +457,32 @@
     <t>cardStateTextDurationMs</t>
   </si>
   <si>
-    <t>卡片状态文本动画时间</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡片状态文本动画时间</t>
+    </r>
   </si>
   <si>
     <t>cardStateTextFloatPx</t>
   </si>
   <si>
-    <t>卡片状态文本浮动高度</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡片状态文本浮动高度</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">##======== </t>
     </r>
     <r>
@@ -541,7 +535,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -568,12 +562,6 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1066,153 +1054,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1235,9 +1223,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2116,7 +2101,7 @@
       <c r="C28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E28" s="8">
@@ -2148,7 +2133,7 @@
       <c r="C30" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="7" t="s">
         <v>53</v>
       </c>
       <c r="E30" s="8">
@@ -2164,7 +2149,7 @@
       <c r="C31" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E31" s="8">

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>##var#column</t>
   </si>
@@ -95,6 +95,62 @@
     </r>
   </si>
   <si>
+    <t>mapDefinitionPath</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图定义</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>路径（相对于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Assets/GameMain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>MapDefinition.asset</t>
+  </si>
+  <si>
     <t>escapeProtectionMs</t>
   </si>
   <si>
@@ -107,6 +163,76 @@
       </rPr>
       <t>逃跑返回地图后的保护时间，毫秒</t>
     </r>
+  </si>
+  <si>
+    <t>lowThreatEnemyPartyEntity</t>
+  </si>
+  <si>
+    <t>string#ref=TbEntityConfig</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低威胁敌人小队实体</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyPartyLowThreat</t>
+  </si>
+  <si>
+    <t>middleThreatEnemyPartyEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中威胁敌人小队实体</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyPartyMiddleThreat</t>
+  </si>
+  <si>
+    <t>highThreatEnemyPartyEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高威胁敌人小队实体</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyPartyHighThreat</t>
+  </si>
+  <si>
+    <t>evacuatePointEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>撤离点实体</t>
+    </r>
+  </si>
+  <si>
+    <t>EvacuatePoint</t>
   </si>
   <si>
     <r>
@@ -535,7 +661,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -717,13 +843,18 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF375623"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF375623"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -928,7 +1059,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -948,6 +1079,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFA9D18E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1075,7 +1221,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1087,34 +1233,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1200,7 +1346,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1222,6 +1368,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1695,13 +1844,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.0073529411765" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1617647058824" style="1" customWidth="1"/>
+    <col min="4" max="4" width="39.8235294117647" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.2794117647059" style="2" customWidth="1"/>
     <col min="6" max="6" width="28" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -1773,81 +1922,93 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:6">
+      <c r="A6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="D6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="8">
         <v>2000</v>
       </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8">
-        <v>3000</v>
+        <v>21</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="8">
-        <v>180</v>
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="F9" s="7"/>
     </row>
     <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="7"/>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="7"/>
@@ -1859,7 +2020,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1869,128 +2030,128 @@
     </row>
     <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E13" s="8">
-        <v>120</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" customHeight="1" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="F14" s="7"/>
     </row>
     <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E15" s="8">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16" s="7"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4</v>
-      </c>
-      <c r="F17" s="7"/>
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E18" s="8">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F18" s="7"/>
     </row>
     <row r="19" customHeight="1" spans="1:6">
-      <c r="A19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
+      <c r="C19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="8">
+        <v>30</v>
+      </c>
       <c r="F19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5</v>
+      </c>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E21" s="8">
         <v>1</v>
@@ -1999,197 +2160,263 @@
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E22" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="7"/>
     </row>
     <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E23" s="8">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="F23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="7" t="s">
-        <v>39</v>
-      </c>
+      <c r="A24" s="7"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="8" t="b">
-        <v>0</v>
-      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="7"/>
     </row>
     <row r="25" customHeight="1" spans="1:6">
-      <c r="A25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7"/>
+      <c r="A25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="8" t="b">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:6">
       <c r="A27" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="8" t="b">
+        <v>53</v>
+      </c>
+      <c r="E27" s="8">
         <v>1</v>
       </c>
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E28" s="8">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F28" s="7"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="8">
-        <v>600</v>
+        <v>58</v>
+      </c>
+      <c r="E29" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="8">
-        <v>600</v>
+        <v>60</v>
+      </c>
+      <c r="E30" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:6">
+      <c r="A32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="8">
-        <v>32</v>
-      </c>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:6">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:6">
-      <c r="A33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="5"/>
+      <c r="D33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="8">
+        <v>600</v>
+      </c>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="E34" s="8">
+        <v>600</v>
       </c>
       <c r="F34" s="7"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:6">
+      <c r="A35" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="8">
+        <v>600</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:6">
+      <c r="A36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="8">
+        <v>32</v>
+      </c>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:6">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:6">
+      <c r="A39" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/GlobalConfig_全局配置.xlsx
+++ b/数据表/Datas/GlobalConfig_全局配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
   <si>
     <t>##var#column</t>
   </si>
@@ -48,7 +53,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>单局与撤离</t>
@@ -57,7 +62,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ==========</t>
@@ -74,7 +79,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>单局时间上限，毫秒</t>
@@ -88,7 +93,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>小地图标记撤离点的时间，毫秒</t>
@@ -105,7 +110,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>地图定义</t>
@@ -114,7 +119,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>SO</t>
@@ -123,7 +128,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>路径（相对于</t>
@@ -132,7 +137,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>Assets/GameMain</t>
@@ -141,7 +146,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -158,7 +163,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>逃跑返回地图后的保护时间，毫秒</t>
@@ -175,7 +180,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>低威胁敌人小队实体</t>
@@ -192,7 +197,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>中威胁敌人小队实体</t>
@@ -209,7 +214,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>高威胁敌人小队实体</t>
@@ -225,7 +230,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>撤离点实体</t>
@@ -235,6 +240,40 @@
     <t>EvacuatePoint</t>
   </si>
   <si>
+    <t>characterLeaderEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家队伍领队实体</t>
+    </r>
+  </si>
+  <si>
+    <t>CharacterLeader</t>
+  </si>
+  <si>
+    <t>CharacterRetinueEntity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家队伍其他实体</t>
+    </r>
+  </si>
+  <si>
+    <t>CharacterRetinue</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">##======== </t>
     </r>
@@ -242,7 +281,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人警惕与追击</t>
@@ -251,7 +290,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ==========</t>
@@ -265,7 +304,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人丢失目标后返回巡逻的时间，毫秒</t>
@@ -279,7 +318,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人正面视野角度</t>
@@ -293,7 +332,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>警惕值满值</t>
@@ -307,7 +346,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>队伍与库存</t>
@@ -316,7 +355,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ==========</t>
@@ -330,7 +369,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>仓库格子数</t>
@@ -344,7 +383,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>共享背包格子数</t>
@@ -358,7 +397,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>保险箱格子数</t>
@@ -372,7 +411,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>最少出战人数</t>
@@ -386,7 +425,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>最多出战人数</t>
@@ -400,7 +439,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人队伍人数上限</t>
@@ -414,7 +453,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>战斗与计时</t>
@@ -423,7 +462,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ==========</t>
@@ -437,7 +476,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>非全员阵亡结算时阵亡角色恢复</t>
@@ -446,7 +485,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>HP</t>
@@ -460,7 +499,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>非全员阵亡结算时阵亡角色恢复</t>
@@ -469,7 +508,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>MP</t>
@@ -483,7 +522,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>逃跑成功率，千分比原型初值</t>
@@ -500,7 +539,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>首版墙体是否阻挡警惕视野</t>
@@ -514,7 +553,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>战斗中是否暂停单局计时</t>
@@ -528,7 +567,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>打开背包是否暂停单局计时</t>
@@ -542,7 +581,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>暂停菜单是否暂停单局计时</t>
@@ -556,7 +595,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人自动行动间隔</t>
@@ -573,7 +612,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>时间注册超时帧数</t>
@@ -587,7 +626,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>卡片状态文本动画时间</t>
@@ -601,7 +640,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>卡片状态文本浮动高度</t>
@@ -615,7 +654,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>新存档</t>
@@ -624,7 +663,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF375623"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> ==========</t>
@@ -641,7 +680,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>新存档直接拥有的角色</t>
@@ -669,25 +708,25 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF375623"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -843,19 +882,19 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF375623"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1346,7 +1385,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1371,6 +1410,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1844,14 +1886,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="34" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.0073529411765" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.1617647058824" style="1" customWidth="1"/>
-    <col min="4" max="4" width="39.8235294117647" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.2794117647059" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.0083333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="39.825" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.2833333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="28" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -2011,136 +2053,128 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" customHeight="1" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A13" s="7"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:6">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="D16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="8">
         <v>3000</v>
       </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:6">
-      <c r="A14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:6">
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="D17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="8">
         <v>180</v>
       </c>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1000</v>
-      </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E18" s="8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="7"/>
     </row>
     <row r="19" customHeight="1" spans="1:6">
-      <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
+      <c r="A19" s="7"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="8">
-        <v>30</v>
-      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="7"/>
     </row>
     <row r="20" customHeight="1" spans="1:6">
-      <c r="A20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="8">
-        <v>5</v>
-      </c>
-      <c r="F20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="7" t="s">
@@ -2154,7 +2188,7 @@
         <v>44</v>
       </c>
       <c r="E21" s="8">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F21" s="7"/>
     </row>
@@ -2170,7 +2204,7 @@
         <v>46</v>
       </c>
       <c r="E22" s="8">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F22" s="7"/>
     </row>
@@ -2186,75 +2220,75 @@
         <v>48</v>
       </c>
       <c r="E23" s="8">
+        <v>5</v>
+      </c>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:6">
+      <c r="A24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:6">
+      <c r="A25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="8">
         <v>4</v>
       </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:6">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:6">
-      <c r="A25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E26" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" customHeight="1" spans="1:6">
-      <c r="A27" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="A27" s="7"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1</v>
-      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="7"/>
     </row>
     <row r="28" customHeight="1" spans="1:6">
-      <c r="A28" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="8">
-        <v>500</v>
-      </c>
-      <c r="F28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="7" t="s">
@@ -2262,61 +2296,61 @@
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="8" t="b">
-        <v>0</v>
+      <c r="E29" s="8">
+        <v>1</v>
       </c>
       <c r="F29" s="7"/>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="8" t="b">
+        <v>59</v>
+      </c>
+      <c r="E30" s="8">
         <v>1</v>
       </c>
       <c r="F30" s="7"/>
     </row>
     <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="8" t="b">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="E31" s="8">
+        <v>500</v>
       </c>
       <c r="F31" s="7"/>
     </row>
     <row r="32" customHeight="1" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E32" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="7"/>
     </row>
@@ -2326,13 +2360,13 @@
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="8">
-        <v>600</v>
+      <c r="E33" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F33" s="7"/>
     </row>
@@ -2342,13 +2376,13 @@
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="8">
-        <v>600</v>
+      <c r="E34" s="8" t="b">
+        <v>0</v>
       </c>
       <c r="F34" s="7"/>
     </row>
@@ -2358,13 +2392,13 @@
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="8">
-        <v>600</v>
+      <c r="E35" s="8" t="b">
+        <v>1</v>
       </c>
       <c r="F35" s="7"/>
     </row>
@@ -2380,43 +2414,91 @@
         <v>72</v>
       </c>
       <c r="E36" s="8">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="F36" s="7"/>
     </row>
     <row r="37" customHeight="1" spans="1:6">
-      <c r="A37" s="7"/>
+      <c r="A37" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="8"/>
+      <c r="C37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="8">
+        <v>600</v>
+      </c>
       <c r="F37" s="7"/>
     </row>
     <row r="38" customHeight="1" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" s="8">
+        <v>600</v>
+      </c>
+      <c r="F38" s="7"/>
     </row>
     <row r="39" customHeight="1" spans="1:6">
       <c r="A39" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="E39" s="8">
+        <v>32</v>
       </c>
       <c r="F39" s="7"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:6">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:6">
+      <c r="A41" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:6">
+      <c r="A42" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
